--- a/web-dashboard/data/Inventaire_Parc.xlsx
+++ b/web-dashboard/data/Inventaire_Parc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rdenimal\Documents\App_Novadis\scan_CLT_SRV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://novadis92.sharepoint.com/sites/Novadis/Technique/TECH  SHARE/00_Fiches Récapitulatives Sites/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDF98C8-53C1-4F8D-BD06-1D55B9F6B25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{825651A8-54F1-4AD6-A01B-ACAED71C9B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16605" windowWidth="29040" windowHeight="15720" tabRatio="867" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="867" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recap Projet" sheetId="30" r:id="rId1"/>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="562">
   <si>
     <t>Installateur</t>
   </si>
@@ -582,6 +582,9 @@
   </si>
   <si>
     <t>NOM</t>
+  </si>
+  <si>
+    <t>SRV-ADS5</t>
   </si>
   <si>
     <t>LOCALISATION</t>
@@ -1807,252 +1810,6 @@
   <si>
     <t>Réglage sensibilité détection de mouvement</t>
   </si>
-  <si>
-    <t>Colonne1</t>
-  </si>
-  <si>
-    <t>SRV-CA-STDO</t>
-  </si>
-  <si>
-    <t>SURETE</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>PowerEdge R350</t>
-  </si>
-  <si>
-    <t>Serveur Amadeus 8</t>
-  </si>
-  <si>
-    <t>FW0TDT3</t>
-  </si>
-  <si>
-    <t>24 OCT. 2025</t>
-  </si>
-  <si>
-    <t>Windows Server 2019 Essentials</t>
-  </si>
-  <si>
-    <t>x64</t>
-  </si>
-  <si>
-    <t>Intel ® Xeon® E-2334 CPU @3.40GHz 3.41 GHz</t>
-  </si>
-  <si>
-    <t>16Go</t>
-  </si>
-  <si>
-    <t>446 Go</t>
-  </si>
-  <si>
-    <t>RAID 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELL PERC H755 </t>
-  </si>
-  <si>
-    <t>Broadcom NetXtreme Gigabit Ethernet</t>
-  </si>
-  <si>
-    <t>B8-CB-29-FB-08-5F</t>
-  </si>
-  <si>
-    <t>192.168.1.213</t>
-  </si>
-  <si>
-    <t>Broadcom NetXtreme Gigabit Ethernet #2</t>
-  </si>
-  <si>
-    <t>B8-CB-29-FB-08-60</t>
-  </si>
-  <si>
-    <t>CLT-CA-STDO</t>
-  </si>
-  <si>
-    <t>Précision 3460</t>
-  </si>
-  <si>
-    <t>Client Amadeus 8</t>
-  </si>
-  <si>
-    <t>D1QH514</t>
-  </si>
-  <si>
-    <t>15 JANV. 2027</t>
-  </si>
-  <si>
-    <t>Windows 11 Professionnel</t>
-  </si>
-  <si>
-    <t>X64</t>
-  </si>
-  <si>
-    <t>13th Gen Intel(R) Core(TM) i7-13700   2.10 GHz</t>
-  </si>
-  <si>
-    <t>Intel(R) UHD Graphics 770</t>
-  </si>
-  <si>
-    <t>NVIDIA T1000</t>
-  </si>
-  <si>
-    <t>238 Go</t>
-  </si>
-  <si>
-    <t>PC SN740 NVMe WD 256GB</t>
-  </si>
-  <si>
-    <t>Intel(R) Ethernet Connection (17) I219-LM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CC-96-E5-39-DB-9D</t>
-  </si>
-  <si>
-    <t>192.168.200.212</t>
-  </si>
-  <si>
-    <t>SRV-VID-STDO</t>
-  </si>
-  <si>
-    <t>JT2TJZJ3</t>
-  </si>
-  <si>
-    <t> 15 OCT. 2024</t>
-  </si>
-  <si>
-    <t>Windows Server 2019 Sandard</t>
-  </si>
-  <si>
-    <t>Intel ® Xeon® E-2124 CPU @3.30GHz 3.31 GHz</t>
-  </si>
-  <si>
-    <t>Matrox G200eW3 (Nuvoton) WDDM 2.0</t>
-  </si>
-  <si>
-    <t>223 Go</t>
-  </si>
-  <si>
-    <t>14,9 To</t>
-  </si>
-  <si>
-    <t>Raid 5</t>
-  </si>
-  <si>
-    <t>BOSS-S1 (intégré)</t>
-  </si>
-  <si>
-    <t>PERC H730P Adapter</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> B8-CB-29-CC-A9-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> B8-CB-29-CC-A9-55</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 192.168.1.164</t>
-  </si>
-  <si>
-    <t>CLT-VID-STDO</t>
-  </si>
-  <si>
-    <t>Client VIDEO</t>
-  </si>
-  <si>
-    <t>92QH514</t>
-  </si>
-  <si>
-    <t>CC-96-E5-39-D7-E0</t>
-  </si>
-  <si>
-    <t>LAPTOP-77OIEFCV</t>
-  </si>
-  <si>
-    <t>novadis.local</t>
-  </si>
-  <si>
-    <t>ASUSTeK COMPUTER INC.</t>
-  </si>
-  <si>
-    <t>ASUS Zenbook 14 UM3406HA_UM3406HA</t>
-  </si>
-  <si>
-    <t>time.windows.com,0x9</t>
-  </si>
-  <si>
-    <t>S5N0CX09P39321C</t>
-  </si>
-  <si>
-    <t>Microsoft Windows 11 Professionnel</t>
-  </si>
-  <si>
-    <t>x64-based PC</t>
-  </si>
-  <si>
-    <t>AMD Ryzen 7 8840HS w/ Radeon 780M Graphics      (Cours: 8)</t>
-  </si>
-  <si>
-    <t>31 Go</t>
-  </si>
-  <si>
-    <t>DisplayLink USB Device</t>
-  </si>
-  <si>
-    <t>C: (952.07 Go)</t>
-  </si>
-  <si>
-    <t>Generic MassStorageClass USB Device - 0 Go - SN: 000000002959</t>
-  </si>
-  <si>
-    <t>MTFDKBA1T0QFM-1BD1AABGB - 953.86 Go - SN: 0000_0000_0000_0001_00A0_7524_47CF_9632.</t>
-  </si>
-  <si>
-    <t>MediaTek Wi-Fi 6E MT7922 (RZ616) 160MHz Wireless LAN Card</t>
-  </si>
-  <si>
-    <t>14:AC:60:A3:D4:CB</t>
-  </si>
-  <si>
-    <t>10.0.0.61</t>
-  </si>
-  <si>
-    <t>10.0.0.253</t>
-  </si>
-  <si>
-    <t>VirtualBox Host-Only Ethernet Adapter</t>
-  </si>
-  <si>
-    <t>0A:00:27:00:00:0D</t>
-  </si>
-  <si>
-    <t>192.168.56.1</t>
-  </si>
-  <si>
-    <t>Realtek Gaming USB 2.5GbE Family Controller</t>
-  </si>
-  <si>
-    <t>6C:6E:07:1D:18:67</t>
-  </si>
-  <si>
-    <t>192.168.200.214</t>
-  </si>
-  <si>
-    <t>255.255.254.0</t>
-  </si>
-  <si>
-    <t>192.168.200.1</t>
-  </si>
-  <si>
-    <t>VirtualBox Host-Only Ethernet Adapter #2</t>
-  </si>
-  <si>
-    <t>0A:00:27:00:00:0C</t>
-  </si>
-  <si>
-    <t>192.168.56.2</t>
-  </si>
 </sst>
 </file>
 
@@ -2062,7 +1819,7 @@
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3199,6 +2956,108 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3222,108 +3081,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3540,6 +3297,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3557,13 +3321,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3705,6 +3462,13 @@
       </fill>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -3722,13 +3486,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thick">
-          <color theme="0"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3762,39 +3519,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -3858,6 +3582,39 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -3990,7 +3747,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4057,7 +3814,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4124,7 +3881,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4191,7 +3948,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4258,7 +4015,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4325,7 +4082,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4392,7 +4149,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4459,7 +4216,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4526,7 +4283,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4593,7 +4350,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4660,7 +4417,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4727,7 +4484,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4794,7 +4551,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4861,7 +4618,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4928,7 +4685,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4995,7 +4752,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5062,7 +4819,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5129,7 +4886,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5196,7 +4953,7 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5263,7 +5020,7 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5330,7 +5087,7 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5397,7 +5154,7 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5464,7 +5221,7 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>8</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5531,7 +5288,7 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>838200</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>30480</xdr:rowOff>
+          <xdr:rowOff>28575</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -5753,11 +5510,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau23" displayName="Tableau23" ref="A1:E5" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau23" displayName="Tableau23" ref="A1:E5" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="A1:E5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="DATE" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{5DEF4043-5815-4D96-A476-B2BE874CB19C}" name="INTERVENANTS" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="DATE" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{5DEF4043-5815-4D96-A476-B2BE874CB19C}" name="INTERVENANTS" dataDxfId="34"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="COMMENTAIRES"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Installateur"/>
     <tableColumn id="4" xr3:uid="{71E13FC5-5F51-4DD4-A539-65598EAA9C9F}" name="Num CC "/>
@@ -5767,33 +5524,33 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A95A6209-1B70-443E-94DD-EC0280EE8FAA}" name="Tableau1614" displayName="Tableau1614" ref="A1:F8" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A95A6209-1B70-443E-94DD-EC0280EE8FAA}" name="Tableau1614" displayName="Tableau1614" ref="A1:F8" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="A1:F8" xr:uid="{A95A6209-1B70-443E-94DD-EC0280EE8FAA}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{10302989-DA47-4F9A-831D-E2974FA029B3}" name="ANNEE" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{ADF607E8-2332-4ED7-B4B1-1E4AE95D9922}" name="MAINTENANCE" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{346F14B9-6F07-4EED-9ACF-DC92F9BDBB9F}" name="APPLICATIF (SUPP)" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{D168D9DB-08C6-41FD-A4CE-A8BBF2B957ED}" name="ACCES AU SUPPORT" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{CF36272B-8461-4E86-BFC8-4B628913DA06}" name="INTERVENTION CORRECTIVE" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{0487574F-CC11-4397-AFB0-175DD4DD25E4}" name="COMMENTAIRES" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{10302989-DA47-4F9A-831D-E2974FA029B3}" name="ANNEE" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{ADF607E8-2332-4ED7-B4B1-1E4AE95D9922}" name="MAINTENANCE" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{346F14B9-6F07-4EED-9ACF-DC92F9BDBB9F}" name="APPLICATIF (SUPP)" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{D168D9DB-08C6-41FD-A4CE-A8BBF2B957ED}" name="ACCES AU SUPPORT" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{CF36272B-8461-4E86-BFC8-4B628913DA06}" name="INTERVENTION CORRECTIVE" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{0487574F-CC11-4397-AFB0-175DD4DD25E4}" name="COMMENTAIRES" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tableau10" displayName="Tableau10" ref="A1:B66" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tableau10" displayName="Tableau10" ref="A1:B66" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A1:B66" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="NOM" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Colonne1" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="NOM" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SRV-ADS5" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tableau1" displayName="Tableau1" ref="A1:F33" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Tableau1" displayName="Tableau1" ref="A1:F33" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowBorderDxfId="19">
   <autoFilter ref="A1:F33" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Système" dataDxfId="18"/>
@@ -5828,7 +5585,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tableau7" displayName="Tableau7" ref="A1:F7" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Tableau7" displayName="Tableau7" ref="A1:F7" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Equipement" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{E4E49256-DD14-4B29-8430-F91236906A84}" name="Libellé" dataDxfId="4"/>
@@ -6142,96 +5899,96 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:K80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="37.109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="22.44140625" style="111" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="20.33203125" customWidth="1"/>
-    <col min="10" max="10" width="23.5546875" style="91" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="24.6640625" customWidth="1"/>
-    <col min="12" max="16" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="111" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="23.5703125" style="91" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="12" max="16" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
       <c r="J1" s="91" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-    </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+    </row>
+    <row r="3" spans="1:11" ht="14.25" customHeight="1">
       <c r="A3" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-    </row>
-    <row r="4" spans="1:11" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+    </row>
+    <row r="4" spans="1:11" ht="109.5" customHeight="1">
       <c r="A4" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="128"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-    </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="129" t="s">
+      <c r="B4" s="162"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="162"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="162"/>
+      <c r="I4" s="162"/>
+    </row>
+    <row r="5" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A5" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132" t="s">
+      <c r="C5" s="166"/>
+      <c r="D5" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132" t="s">
+      <c r="E5" s="166"/>
+      <c r="F5" s="166" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
-    </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="130"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="166"/>
+      <c r="I5" s="166"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" customHeight="1">
+      <c r="A6" s="164"/>
       <c r="B6" s="95" t="s">
         <v>9</v>
       </c>
@@ -6249,8 +6006,8 @@
       </c>
       <c r="I6" s="94"/>
     </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="130"/>
+    <row r="7" spans="1:11" ht="15" customHeight="1">
+      <c r="A7" s="164"/>
       <c r="B7" s="95" t="s">
         <v>13</v>
       </c>
@@ -6268,8 +6025,8 @@
       </c>
       <c r="I7" s="94"/>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="130"/>
+    <row r="8" spans="1:11" ht="15" customHeight="1">
+      <c r="A8" s="164"/>
       <c r="B8" s="95" t="s">
         <v>16</v>
       </c>
@@ -6287,8 +6044,8 @@
       </c>
       <c r="I8" s="94"/>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="131"/>
+    <row r="9" spans="1:11" ht="15" customHeight="1">
+      <c r="A9" s="165"/>
       <c r="B9" s="95" t="s">
         <v>18</v>
       </c>
@@ -6306,23 +6063,23 @@
       </c>
       <c r="I9" s="94"/>
     </row>
-    <row r="10" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="59.25" customHeight="1">
       <c r="A10" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="139" t="s">
+      <c r="B10" s="153" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="140"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="154"/>
+      <c r="H10" s="154"/>
+      <c r="I10" s="154"/>
       <c r="J10" s="96"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="90" t="s">
         <v>21</v>
       </c>
@@ -6345,7 +6102,7 @@
       <c r="J11" s="103"/>
       <c r="K11" s="104"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12" s="105" t="s">
         <v>26</v>
       </c>
@@ -6358,7 +6115,7 @@
       <c r="H12" s="107"/>
       <c r="I12" s="108"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13" s="100" t="s">
         <v>27</v>
       </c>
@@ -6371,149 +6128,149 @@
       <c r="H13" s="110"/>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="42" customHeight="1">
       <c r="A14" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="141"/>
-      <c r="C14" s="141"/>
-      <c r="D14" s="141"/>
-      <c r="E14" s="141"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="141"/>
+      <c r="B14" s="155"/>
+      <c r="C14" s="155"/>
+      <c r="D14" s="155"/>
+      <c r="E14" s="155"/>
+      <c r="F14" s="155"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="155"/>
+      <c r="I14" s="155"/>
       <c r="J14" s="103"/>
       <c r="K14" s="104"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="I15" s="112"/>
       <c r="J15" s="103"/>
       <c r="K15" s="104"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="154" t="s">
+    <row r="16" spans="1:11">
+      <c r="A16" s="147" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="142" t="s">
+      <c r="B16" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="142"/>
-      <c r="D16" s="142" t="s">
+      <c r="C16" s="146"/>
+      <c r="D16" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="142"/>
+      <c r="E16" s="146"/>
       <c r="F16" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="143" t="s">
+      <c r="G16" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="144"/>
-      <c r="I16" s="145"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="158"/>
       <c r="J16" s="103"/>
       <c r="K16" s="104"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="155"/>
-      <c r="B17" s="137"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
+    <row r="17" spans="1:9" ht="15" customHeight="1">
+      <c r="A17" s="148"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="150"/>
+      <c r="E17" s="150"/>
       <c r="F17" s="114"/>
-      <c r="G17" s="134"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="136"/>
-    </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="155"/>
-      <c r="B18" s="137"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="145"/>
+    </row>
+    <row r="18" spans="1:9" ht="15" customHeight="1">
+      <c r="A18" s="148"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="152"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="150"/>
       <c r="F18" s="114"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="136"/>
-    </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="155"/>
-      <c r="B19" s="137"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="144"/>
+      <c r="I18" s="145"/>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1">
+      <c r="A19" s="148"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
       <c r="F19" s="114"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="136"/>
-    </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="155"/>
-      <c r="B20" s="137"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="144"/>
+      <c r="I19" s="145"/>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1">
+      <c r="A20" s="148"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="152"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
       <c r="F20" s="114"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="136"/>
-    </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="155"/>
-      <c r="B21" s="137"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="144"/>
+      <c r="I20" s="145"/>
+    </row>
+    <row r="21" spans="1:9" ht="15" customHeight="1">
+      <c r="A21" s="148"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="150"/>
       <c r="F21" s="114"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="136"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="155"/>
-      <c r="B22" s="133"/>
-      <c r="C22" s="133"/>
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="145"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="148"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="142"/>
+      <c r="E22" s="142"/>
       <c r="F22" s="114"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="136"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="155"/>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="145"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="148"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="142"/>
+      <c r="E23" s="142"/>
       <c r="F23" s="114"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="135"/>
-      <c r="I23" s="136"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="155"/>
-      <c r="B24" s="147"/>
-      <c r="C24" s="147"/>
-      <c r="D24" s="146"/>
-      <c r="E24" s="146"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="145"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="148"/>
+      <c r="B24" s="141"/>
+      <c r="C24" s="141"/>
+      <c r="D24" s="142"/>
+      <c r="E24" s="142"/>
       <c r="F24" s="114"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="136"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="156"/>
-      <c r="B25" s="147"/>
-      <c r="C25" s="147"/>
-      <c r="D25" s="146"/>
-      <c r="E25" s="146"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="145"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="149"/>
+      <c r="B25" s="141"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="142"/>
+      <c r="E25" s="142"/>
       <c r="F25" s="114"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="135"/>
-      <c r="I25" s="136"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G25" s="143"/>
+      <c r="H25" s="144"/>
+      <c r="I25" s="145"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="22"/>
       <c r="B26" s="115"/>
       <c r="C26" s="115"/>
@@ -6523,14 +6280,14 @@
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="148" t="s">
+    <row r="27" spans="1:9">
+      <c r="A27" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="149" t="s">
+      <c r="B27" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="150"/>
+      <c r="C27" s="139"/>
       <c r="D27" s="100" t="s">
         <v>35</v>
       </c>
@@ -6540,366 +6297,366 @@
       <c r="F27" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="G27" s="142" t="s">
+      <c r="G27" s="146" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="142"/>
-      <c r="I27" s="142"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="148"/>
-      <c r="B28" s="151" t="s">
+      <c r="H27" s="146"/>
+      <c r="I27" s="146"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="129"/>
+      <c r="B28" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="152"/>
+      <c r="C28" s="134"/>
       <c r="D28" s="116"/>
       <c r="E28" s="93"/>
       <c r="F28" s="93"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="148"/>
-      <c r="B29" s="151" t="s">
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1">
+      <c r="A29" s="129"/>
+      <c r="B29" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="152"/>
+      <c r="C29" s="134"/>
       <c r="D29" s="116"/>
       <c r="E29" s="93"/>
       <c r="F29" s="93"/>
-      <c r="G29" s="153"/>
-      <c r="H29" s="153"/>
-      <c r="I29" s="153"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="148"/>
-      <c r="B30" s="151" t="s">
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
+      <c r="I29" s="125"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="129"/>
+      <c r="B30" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="152"/>
+      <c r="C30" s="134"/>
       <c r="D30" s="116"/>
       <c r="E30" s="93"/>
       <c r="F30" s="93"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="153"/>
-      <c r="I30" s="153"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="148"/>
-      <c r="B31" s="151" t="s">
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="125"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="129"/>
+      <c r="B31" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="152"/>
+      <c r="C31" s="134"/>
       <c r="D31" s="116"/>
       <c r="E31" s="93"/>
       <c r="F31" s="93"/>
-      <c r="G31" s="153"/>
-      <c r="H31" s="153"/>
-      <c r="I31" s="153"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="148"/>
-      <c r="B32" s="151" t="s">
+      <c r="G31" s="125"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="125"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="129"/>
+      <c r="B32" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="152"/>
+      <c r="C32" s="134"/>
       <c r="D32" s="116"/>
       <c r="E32" s="93"/>
       <c r="F32" s="93"/>
-      <c r="G32" s="153"/>
-      <c r="H32" s="153"/>
-      <c r="I32" s="153"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="148"/>
-      <c r="B33" s="151" t="s">
+      <c r="G32" s="125"/>
+      <c r="H32" s="125"/>
+      <c r="I32" s="125"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="129"/>
+      <c r="B33" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="152"/>
+      <c r="C33" s="134"/>
       <c r="D33" s="116"/>
       <c r="E33" s="93"/>
       <c r="F33" s="93"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="153"/>
-      <c r="I33" s="153"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="148"/>
-      <c r="B34" s="151" t="s">
+      <c r="G33" s="125"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="125"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="129"/>
+      <c r="B34" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="152"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="116"/>
       <c r="E34" s="93"/>
       <c r="F34" s="93"/>
-      <c r="G34" s="153"/>
-      <c r="H34" s="153"/>
-      <c r="I34" s="153"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="148"/>
-      <c r="B35" s="151" t="s">
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="125"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="129"/>
+      <c r="B35" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="152"/>
+      <c r="C35" s="134"/>
       <c r="D35" s="116"/>
       <c r="E35" s="93"/>
       <c r="F35" s="93"/>
-      <c r="G35" s="153"/>
-      <c r="H35" s="153"/>
-      <c r="I35" s="153"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="148"/>
-      <c r="B36" s="151" t="s">
+      <c r="G35" s="125"/>
+      <c r="H35" s="125"/>
+      <c r="I35" s="125"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="129"/>
+      <c r="B36" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="152"/>
+      <c r="C36" s="134"/>
       <c r="D36" s="116"/>
       <c r="E36" s="93"/>
       <c r="F36" s="93"/>
-      <c r="G36" s="153"/>
-      <c r="H36" s="153"/>
-      <c r="I36" s="153"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="148"/>
-      <c r="B37" s="151" t="s">
+      <c r="G36" s="125"/>
+      <c r="H36" s="125"/>
+      <c r="I36" s="125"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="129"/>
+      <c r="B37" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="152"/>
+      <c r="C37" s="134"/>
       <c r="D37" s="116"/>
       <c r="E37" s="93"/>
       <c r="F37" s="93"/>
-      <c r="G37" s="153"/>
-      <c r="H37" s="153"/>
-      <c r="I37" s="153"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="148"/>
-      <c r="B38" s="151" t="s">
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
+      <c r="I37" s="125"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="129"/>
+      <c r="B38" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="152"/>
+      <c r="C38" s="134"/>
       <c r="D38" s="116"/>
       <c r="E38" s="93"/>
       <c r="F38" s="93"/>
-      <c r="G38" s="153"/>
-      <c r="H38" s="153"/>
-      <c r="I38" s="153"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="148"/>
-      <c r="B39" s="151" t="s">
+      <c r="G38" s="125"/>
+      <c r="H38" s="125"/>
+      <c r="I38" s="125"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="129"/>
+      <c r="B39" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="152"/>
+      <c r="C39" s="134"/>
       <c r="D39" s="116"/>
       <c r="E39" s="93"/>
       <c r="F39" s="93"/>
-      <c r="G39" s="153"/>
-      <c r="H39" s="153"/>
-      <c r="I39" s="153"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="148"/>
-      <c r="B40" s="151" t="s">
+      <c r="G39" s="125"/>
+      <c r="H39" s="125"/>
+      <c r="I39" s="125"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="129"/>
+      <c r="B40" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="152"/>
+      <c r="C40" s="134"/>
       <c r="D40" s="116"/>
       <c r="E40" s="93"/>
       <c r="F40" s="93"/>
-      <c r="G40" s="153"/>
-      <c r="H40" s="153"/>
-      <c r="I40" s="153"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="148"/>
-      <c r="B41" s="151" t="s">
+      <c r="G40" s="125"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="125"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="129"/>
+      <c r="B41" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="152"/>
+      <c r="C41" s="134"/>
       <c r="D41" s="116"/>
       <c r="E41" s="93"/>
       <c r="F41" s="93"/>
-      <c r="G41" s="153"/>
-      <c r="H41" s="153"/>
-      <c r="I41" s="153"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="148"/>
-      <c r="B42" s="151" t="s">
+      <c r="G41" s="125"/>
+      <c r="H41" s="125"/>
+      <c r="I41" s="125"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="129"/>
+      <c r="B42" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="152"/>
+      <c r="C42" s="134"/>
       <c r="D42" s="116"/>
       <c r="E42" s="93"/>
       <c r="F42" s="93"/>
-      <c r="G42" s="153"/>
-      <c r="H42" s="153"/>
-      <c r="I42" s="153"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="148"/>
-      <c r="B43" s="151" t="s">
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="129"/>
+      <c r="B43" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="152"/>
+      <c r="C43" s="134"/>
       <c r="D43" s="116"/>
       <c r="E43" s="93"/>
       <c r="F43" s="93"/>
-      <c r="G43" s="153"/>
-      <c r="H43" s="153"/>
-      <c r="I43" s="153"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="148"/>
-      <c r="B44" s="151" t="s">
+      <c r="G43" s="125"/>
+      <c r="H43" s="125"/>
+      <c r="I43" s="125"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="129"/>
+      <c r="B44" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="152"/>
+      <c r="C44" s="134"/>
       <c r="D44" s="116"/>
       <c r="E44" s="93"/>
       <c r="F44" s="93"/>
-      <c r="G44" s="153"/>
-      <c r="H44" s="153"/>
-      <c r="I44" s="153"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="148"/>
-      <c r="B45" s="151" t="s">
+      <c r="G44" s="125"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="125"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="129"/>
+      <c r="B45" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="152"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="116"/>
       <c r="E45" s="93"/>
       <c r="F45" s="93"/>
-      <c r="G45" s="153"/>
-      <c r="H45" s="153"/>
-      <c r="I45" s="153"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="148"/>
-      <c r="B46" s="151" t="s">
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="125"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="129"/>
+      <c r="B46" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="152"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="116"/>
       <c r="E46" s="93"/>
       <c r="F46" s="93"/>
-      <c r="G46" s="153"/>
-      <c r="H46" s="153"/>
-      <c r="I46" s="153"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="148"/>
-      <c r="B47" s="151" t="s">
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="125"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="129"/>
+      <c r="B47" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="152"/>
+      <c r="C47" s="134"/>
       <c r="D47" s="116"/>
       <c r="E47" s="93"/>
       <c r="F47" s="93"/>
-      <c r="G47" s="153"/>
-      <c r="H47" s="153"/>
-      <c r="I47" s="153"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="148"/>
-      <c r="B48" s="157" t="s">
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
+      <c r="I47" s="125"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="129"/>
+      <c r="B48" s="131" t="s">
         <v>59</v>
       </c>
-      <c r="C48" s="158"/>
+      <c r="C48" s="132"/>
       <c r="D48" s="116"/>
       <c r="E48" s="93"/>
       <c r="F48" s="93"/>
-      <c r="G48" s="153"/>
-      <c r="H48" s="153"/>
-      <c r="I48" s="153"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="148"/>
-      <c r="B49" s="151" t="s">
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="125"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="129"/>
+      <c r="B49" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="152"/>
+      <c r="C49" s="134"/>
       <c r="D49" s="116"/>
       <c r="E49" s="93"/>
       <c r="F49" s="93"/>
-      <c r="G49" s="153"/>
-      <c r="H49" s="153"/>
-      <c r="I49" s="153"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
+      <c r="I49" s="125"/>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="117"/>
       <c r="C50" s="118"/>
       <c r="D50" s="118"/>
       <c r="E50" s="111"/>
       <c r="F50" s="119"/>
-      <c r="G50" s="159"/>
-      <c r="H50" s="159"/>
-      <c r="I50" s="159"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="160" t="s">
+      <c r="G50" s="135"/>
+      <c r="H50" s="135"/>
+      <c r="I50" s="135"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="136" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="149" t="s">
+      <c r="B51" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="150"/>
+      <c r="C51" s="139"/>
       <c r="D51" s="100" t="s">
         <v>63</v>
       </c>
       <c r="E51" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="F51" s="149" t="s">
+      <c r="F51" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="G51" s="162"/>
-      <c r="H51" s="162"/>
-      <c r="I51" s="162"/>
-    </row>
-    <row r="52" spans="1:10" s="121" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="160"/>
-      <c r="B52" s="163"/>
-      <c r="C52" s="164"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="140"/>
+      <c r="I51" s="140"/>
+    </row>
+    <row r="52" spans="1:10" s="121" customFormat="1" ht="15" customHeight="1">
+      <c r="A52" s="136"/>
+      <c r="B52" s="126"/>
+      <c r="C52" s="127"/>
       <c r="D52" s="116"/>
       <c r="E52" s="116"/>
-      <c r="F52" s="165"/>
-      <c r="G52" s="165"/>
-      <c r="H52" s="165"/>
-      <c r="I52" s="165"/>
+      <c r="F52" s="128"/>
+      <c r="G52" s="128"/>
+      <c r="H52" s="128"/>
+      <c r="I52" s="128"/>
       <c r="J52" s="120"/>
     </row>
-    <row r="53" spans="1:10" s="121" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="160"/>
-      <c r="B53" s="163"/>
-      <c r="C53" s="164"/>
+    <row r="53" spans="1:10" s="121" customFormat="1">
+      <c r="A53" s="136"/>
+      <c r="B53" s="126"/>
+      <c r="C53" s="127"/>
       <c r="D53" s="116"/>
       <c r="E53" s="116"/>
-      <c r="F53" s="165"/>
-      <c r="G53" s="165"/>
-      <c r="H53" s="165"/>
-      <c r="I53" s="165"/>
+      <c r="F53" s="128"/>
+      <c r="G53" s="128"/>
+      <c r="H53" s="128"/>
+      <c r="I53" s="128"/>
       <c r="J53" s="120"/>
     </row>
-    <row r="54" spans="1:10" s="121" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="161"/>
-      <c r="B54" s="163"/>
-      <c r="C54" s="164"/>
+    <row r="54" spans="1:10" s="121" customFormat="1">
+      <c r="A54" s="137"/>
+      <c r="B54" s="126"/>
+      <c r="C54" s="127"/>
       <c r="D54" s="116"/>
       <c r="E54" s="116"/>
-      <c r="F54" s="165"/>
-      <c r="G54" s="165"/>
-      <c r="H54" s="165"/>
-      <c r="I54" s="165"/>
+      <c r="F54" s="128"/>
+      <c r="G54" s="128"/>
+      <c r="H54" s="128"/>
+      <c r="I54" s="128"/>
       <c r="J54" s="120"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="117"/>
       <c r="C55" s="118"/>
       <c r="D55" s="118"/>
@@ -6909,8 +6666,8 @@
       <c r="H55" s="119"/>
       <c r="I55" s="119"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="148" t="s">
+    <row r="56" spans="1:10">
+      <c r="A56" s="129" t="s">
         <v>65</v>
       </c>
       <c r="B56" s="100" t="s">
@@ -6922,119 +6679,119 @@
       <c r="D56" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="E56" s="166" t="s">
+      <c r="E56" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="F56" s="166"/>
-      <c r="G56" s="166"/>
-      <c r="H56" s="166"/>
-      <c r="I56" s="166"/>
+      <c r="F56" s="130"/>
+      <c r="G56" s="130"/>
+      <c r="H56" s="130"/>
+      <c r="I56" s="130"/>
       <c r="J56" s="91" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="148"/>
+    <row r="57" spans="1:10">
+      <c r="A57" s="129"/>
       <c r="B57" s="122" t="s">
         <v>70</v>
       </c>
       <c r="C57" s="123"/>
       <c r="D57" s="39"/>
-      <c r="E57" s="153"/>
-      <c r="F57" s="153"/>
-      <c r="G57" s="153"/>
-      <c r="H57" s="153"/>
-      <c r="I57" s="153"/>
+      <c r="E57" s="125"/>
+      <c r="F57" s="125"/>
+      <c r="G57" s="125"/>
+      <c r="H57" s="125"/>
+      <c r="I57" s="125"/>
       <c r="J57" s="91" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="148"/>
+    <row r="58" spans="1:10">
+      <c r="A58" s="129"/>
       <c r="B58" s="122" t="s">
         <v>71</v>
       </c>
       <c r="C58" s="123"/>
       <c r="D58" s="123"/>
-      <c r="E58" s="153"/>
-      <c r="F58" s="153"/>
-      <c r="G58" s="153"/>
-      <c r="H58" s="153"/>
-      <c r="I58" s="153"/>
+      <c r="E58" s="125"/>
+      <c r="F58" s="125"/>
+      <c r="G58" s="125"/>
+      <c r="H58" s="125"/>
+      <c r="I58" s="125"/>
       <c r="J58" s="91" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="148"/>
+    <row r="59" spans="1:10">
+      <c r="A59" s="129"/>
       <c r="B59" s="122" t="s">
         <v>69</v>
       </c>
       <c r="C59" s="123"/>
       <c r="D59" s="123"/>
-      <c r="E59" s="153"/>
-      <c r="F59" s="153"/>
-      <c r="G59" s="153"/>
-      <c r="H59" s="153"/>
-      <c r="I59" s="153"/>
+      <c r="E59" s="125"/>
+      <c r="F59" s="125"/>
+      <c r="G59" s="125"/>
+      <c r="H59" s="125"/>
+      <c r="I59" s="125"/>
       <c r="J59" s="91" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="148"/>
+    <row r="60" spans="1:10">
+      <c r="A60" s="129"/>
       <c r="B60" s="122" t="s">
         <v>69</v>
       </c>
       <c r="C60" s="123"/>
       <c r="D60" s="123"/>
-      <c r="E60" s="153"/>
-      <c r="F60" s="153"/>
-      <c r="G60" s="153"/>
-      <c r="H60" s="153"/>
-      <c r="I60" s="153"/>
+      <c r="E60" s="125"/>
+      <c r="F60" s="125"/>
+      <c r="G60" s="125"/>
+      <c r="H60" s="125"/>
+      <c r="I60" s="125"/>
       <c r="J60" s="91" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="148"/>
+    <row r="61" spans="1:10">
+      <c r="A61" s="129"/>
       <c r="B61" s="122" t="s">
         <v>69</v>
       </c>
       <c r="C61" s="123"/>
       <c r="D61" s="39"/>
-      <c r="E61" s="153"/>
-      <c r="F61" s="153"/>
-      <c r="G61" s="153"/>
-      <c r="H61" s="153"/>
-      <c r="I61" s="153"/>
+      <c r="E61" s="125"/>
+      <c r="F61" s="125"/>
+      <c r="G61" s="125"/>
+      <c r="H61" s="125"/>
+      <c r="I61" s="125"/>
       <c r="J61" s="91" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="117"/>
       <c r="J62" s="91" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="J63" s="91" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="J64" s="91" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10">
       <c r="J65" s="91" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10">
       <c r="B66" s="119"/>
       <c r="C66" s="15"/>
       <c r="D66" s="15"/>
@@ -7047,7 +6804,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10">
       <c r="B67" s="119"/>
       <c r="C67" s="15"/>
       <c r="D67" s="15"/>
@@ -7057,7 +6814,7 @@
       <c r="H67" s="15"/>
       <c r="I67" s="15"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10">
       <c r="B68" s="119"/>
       <c r="C68" s="15"/>
       <c r="D68" s="15"/>
@@ -7067,7 +6824,7 @@
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10">
       <c r="B69" s="119"/>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
@@ -7077,7 +6834,7 @@
       <c r="H69" s="15"/>
       <c r="I69" s="15"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10">
       <c r="B70" s="119"/>
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
@@ -7087,7 +6844,7 @@
       <c r="H70" s="15"/>
       <c r="I70" s="15"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10">
       <c r="B71" s="119"/>
       <c r="C71" s="15"/>
       <c r="D71" s="15"/>
@@ -7097,7 +6854,7 @@
       <c r="H71" s="15"/>
       <c r="I71" s="15"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10">
       <c r="B72" s="119"/>
       <c r="C72" s="15"/>
       <c r="D72" s="15"/>
@@ -7107,7 +6864,7 @@
       <c r="H72" s="15"/>
       <c r="I72" s="15"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10">
       <c r="B73" s="119"/>
       <c r="C73" s="15"/>
       <c r="D73" s="15"/>
@@ -7117,7 +6874,7 @@
       <c r="H73" s="15"/>
       <c r="I73" s="15"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10">
       <c r="B74" s="119"/>
       <c r="C74" s="15"/>
       <c r="D74" s="15"/>
@@ -7127,7 +6884,7 @@
       <c r="H74" s="15"/>
       <c r="I74" s="15"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10">
       <c r="B75" s="119"/>
       <c r="C75" s="15"/>
       <c r="D75" s="15"/>
@@ -7137,7 +6894,7 @@
       <c r="H75" s="15"/>
       <c r="I75" s="15"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10">
       <c r="B76" s="119"/>
       <c r="C76" s="15"/>
       <c r="D76" s="15"/>
@@ -7147,7 +6904,7 @@
       <c r="H76" s="15"/>
       <c r="I76" s="15"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10">
       <c r="B77" s="119"/>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
@@ -7157,7 +6914,7 @@
       <c r="H77" s="15"/>
       <c r="I77" s="15"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10">
       <c r="B78" s="119"/>
       <c r="C78" s="15"/>
       <c r="D78" s="15"/>
@@ -7167,7 +6924,7 @@
       <c r="H78" s="15"/>
       <c r="I78" s="15"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10">
       <c r="B79" s="119"/>
       <c r="C79" s="15"/>
       <c r="D79" s="15"/>
@@ -7177,7 +6934,7 @@
       <c r="H79" s="15"/>
       <c r="I79" s="15"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10">
       <c r="B80" s="119"/>
       <c r="C80" s="15"/>
       <c r="D80" s="15"/>
@@ -7189,50 +6946,43 @@
     </row>
   </sheetData>
   <mergeCells count="105">
-    <mergeCell ref="E61:I61"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="E56:I56"/>
-    <mergeCell ref="E57:I57"/>
-    <mergeCell ref="E58:I58"/>
-    <mergeCell ref="E59:I59"/>
-    <mergeCell ref="E60:I60"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:I22"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="G25:I25"/>
@@ -7257,43 +7007,50 @@
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="E61:I61"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="E56:I56"/>
+    <mergeCell ref="E57:I57"/>
+    <mergeCell ref="E58:I58"/>
+    <mergeCell ref="E59:I59"/>
+    <mergeCell ref="E60:I60"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B57:B61" xr:uid="{DE5F0C72-FF19-4C19-9AAC-1DA4927D9237}">
@@ -7322,7 +7079,7 @@
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7344,7 +7101,7 @@
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7366,7 +7123,7 @@
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7388,7 +7145,7 @@
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7410,7 +7167,7 @@
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7432,7 +7189,7 @@
                     <xdr:col>2</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7454,7 +7211,7 @@
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7476,7 +7233,7 @@
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7498,7 +7255,7 @@
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7520,7 +7277,7 @@
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7542,7 +7299,7 @@
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7564,7 +7321,7 @@
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7586,7 +7343,7 @@
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7608,7 +7365,7 @@
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7630,7 +7387,7 @@
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7652,7 +7409,7 @@
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7674,7 +7431,7 @@
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7696,7 +7453,7 @@
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7718,7 +7475,7 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7740,7 +7497,7 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>6</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7762,7 +7519,7 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7784,7 +7541,7 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7806,7 +7563,7 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>8</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7828,7 +7585,7 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>838200</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>30480</xdr:rowOff>
+                    <xdr:rowOff>28575</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7847,148 +7604,148 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:K24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22.5546875" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="29.109375" customWidth="1"/>
-    <col min="9" max="9" width="27.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.6640625" customWidth="1"/>
-    <col min="11" max="11" width="24.5546875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" customWidth="1"/>
+    <col min="9" max="9" width="27.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.5703125" style="15" customWidth="1"/>
     <col min="12" max="15" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="15" customFormat="1">
       <c r="A1" s="15" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="H2" s="15"/>
       <c r="I2"/>
       <c r="K2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="H3" s="15"/>
       <c r="I3"/>
       <c r="K3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="H4" s="15"/>
       <c r="K4"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="H5" s="15"/>
       <c r="K5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="H6" s="15"/>
       <c r="K6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="H7" s="15"/>
       <c r="K7"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="H8" s="15"/>
       <c r="K8"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="H9" s="15"/>
       <c r="K9"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="H10" s="15"/>
       <c r="K10"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="H11" s="15"/>
       <c r="K11"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="H12" s="15"/>
       <c r="K12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="H13" s="15"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="H14" s="15"/>
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="H15" s="15"/>
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="H16" s="15"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:11">
       <c r="H17" s="15"/>
       <c r="K17"/>
     </row>
-    <row r="18" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:11">
       <c r="H18" s="15"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="8:11">
       <c r="H19" s="15"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:11">
       <c r="H20" s="15"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="8:11">
       <c r="H21" s="15"/>
       <c r="K21"/>
     </row>
-    <row r="22" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="8:11">
       <c r="H22" s="15"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="8:11">
       <c r="H23" s="15"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="8:11">
       <c r="H24" s="15"/>
       <c r="K24"/>
     </row>
@@ -8006,32 +7763,32 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="34.88671875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="32.5546875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="29.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.44140625" style="15" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="15"/>
+    <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.42578125" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="11.42578125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="76" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F1" s="78" t="s">
         <v>38</v>
@@ -8039,7 +7796,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="20"/>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -8047,7 +7804,7 @@
       <c r="E2" s="39"/>
       <c r="F2" s="79"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" s="20"/>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -8055,7 +7812,7 @@
       <c r="E3" s="39"/>
       <c r="F3" s="79"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="20"/>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
@@ -8063,7 +7820,7 @@
       <c r="E4" s="39"/>
       <c r="F4" s="79"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" s="20"/>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
@@ -8071,19 +7828,19 @@
       <c r="E5" s="39"/>
       <c r="F5" s="79"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="79" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="80"/>
       <c r="B7" s="81"/>
       <c r="C7" s="81"/>
@@ -8091,264 +7848,264 @@
       <c r="E7" s="81"/>
       <c r="F7" s="82"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="39"/>
       <c r="B12" s="39"/>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="F12" s="39"/>
       <c r="G12" s="39" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="39"/>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="39" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="39"/>
       <c r="B14" s="39"/>
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
       <c r="F14" s="39"/>
       <c r="G14" s="39" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="39"/>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
       <c r="D15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="39"/>
       <c r="B16" s="39"/>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
       <c r="F16" s="39"/>
       <c r="G16" s="39" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="39"/>
       <c r="B17" s="39"/>
       <c r="C17" s="39"/>
       <c r="D17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="39" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="39"/>
       <c r="B18" s="39"/>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
       <c r="F18" s="39"/>
       <c r="G18" s="39" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="39"/>
       <c r="B19" s="39"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
       <c r="F19" s="39"/>
       <c r="G19" s="39" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="39"/>
       <c r="B20" s="39"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
       <c r="F20" s="39"/>
       <c r="G20" s="39" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="39"/>
       <c r="B21" s="39"/>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
       <c r="F21" s="39"/>
       <c r="G21" s="39" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="39"/>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
       <c r="F22" s="39"/>
       <c r="G22" s="39" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="39"/>
       <c r="B23" s="39"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
       <c r="F23" s="39"/>
       <c r="G23" s="39" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="39"/>
       <c r="B24" s="39"/>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="39" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="39"/>
       <c r="B25" s="39"/>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="39"/>
       <c r="B26" s="39"/>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
       <c r="F26" s="39"/>
       <c r="G26" s="39" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="39"/>
       <c r="B27" s="39"/>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
       <c r="F27" s="39"/>
       <c r="G27" s="39" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="39"/>
       <c r="B28" s="39"/>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
       <c r="F28" s="39"/>
       <c r="G28" s="39" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="39"/>
       <c r="B29" s="39"/>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="F29" s="39"/>
       <c r="G29" s="39" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="39"/>
       <c r="B30" s="39"/>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="F30" s="39"/>
       <c r="G30" s="39" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="39"/>
       <c r="B31" s="39"/>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
       <c r="F31" s="39"/>
       <c r="G31" s="39" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="39"/>
       <c r="B32" s="39"/>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
       <c r="F32" s="39"/>
       <c r="G32" s="39" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="39"/>
       <c r="B33" s="39"/>
       <c r="C33" s="39"/>
       <c r="D33" s="39"/>
       <c r="F33" s="39"/>
       <c r="G33" s="39" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="39"/>
       <c r="B34" s="39"/>
       <c r="C34" s="39"/>
       <c r="D34" s="39"/>
       <c r="F34" s="39"/>
       <c r="G34" s="39" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="39"/>
       <c r="B35" s="39"/>
       <c r="C35" s="39"/>
       <c r="D35" s="39"/>
       <c r="F35" s="39"/>
       <c r="G35" s="39" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -8367,44 +8124,44 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="27" style="15" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5546875" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" customWidth="1"/>
-    <col min="6" max="6" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.88671875" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.44140625" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="86" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="86" customFormat="1" ht="15.75">
       <c r="A1" s="83" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C1" s="83" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D1" s="83" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E1" s="83" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F1" s="83" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G1" s="83" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1" s="84" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I1" s="83" t="s">
         <v>38</v>
@@ -8412,9 +8169,9 @@
       <c r="J1" s="85"/>
       <c r="K1" s="85"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -8425,9 +8182,9 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -8438,7 +8195,7 @@
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4" s="39"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -8449,7 +8206,7 @@
       <c r="H4" s="17"/>
       <c r="I4" s="17"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="39"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -8460,7 +8217,7 @@
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" s="39"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -8471,7 +8228,7 @@
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7" s="39"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -8482,7 +8239,7 @@
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8" s="39"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -8506,68 +8263,68 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:O30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="28.109375" customWidth="1"/>
-    <col min="3" max="3" width="30.44140625" customWidth="1"/>
-    <col min="4" max="4" width="38.44140625" customWidth="1"/>
-    <col min="6" max="6" width="24.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" customWidth="1"/>
-    <col min="9" max="9" width="22.44140625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="24.5546875" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" customWidth="1"/>
+    <col min="9" max="9" width="22.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="24.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="18.399999999999999" thickBot="1">
       <c r="A1" s="43" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F1" s="44" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G1" s="44" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1" s="44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I1" s="44" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J1" s="44" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K1" s="44" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L1" s="44" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O1" s="45" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="18.399999999999999" thickBot="1">
       <c r="A2" s="174">
         <v>1</v>
       </c>
@@ -8586,707 +8343,707 @@
       <c r="N2" s="178"/>
       <c r="O2" s="179"/>
     </row>
-    <row r="3" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="21">
       <c r="A3" s="175"/>
       <c r="B3" s="180"/>
       <c r="C3" s="183"/>
       <c r="D3" s="186"/>
       <c r="E3" s="46" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="48"/>
       <c r="I3" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J3" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K3" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L3" s="51"/>
       <c r="M3" s="49"/>
       <c r="N3" s="49"/>
       <c r="O3" s="52"/>
     </row>
-    <row r="4" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="21">
       <c r="A4" s="175"/>
       <c r="B4" s="181"/>
       <c r="C4" s="184"/>
       <c r="D4" s="187"/>
       <c r="E4" s="46" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="47"/>
       <c r="H4" s="48"/>
       <c r="I4" s="49" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J4" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K4" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L4" s="51"/>
       <c r="M4" s="50"/>
       <c r="N4" s="50"/>
       <c r="O4" s="52"/>
     </row>
-    <row r="5" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="21">
       <c r="A5" s="175"/>
       <c r="B5" s="181"/>
       <c r="C5" s="184"/>
       <c r="D5" s="187"/>
       <c r="E5" s="46" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F5" s="47"/>
       <c r="G5" s="47"/>
       <c r="H5" s="48"/>
       <c r="I5" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K5" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L5" s="51"/>
       <c r="M5" s="50"/>
       <c r="N5" s="50"/>
       <c r="O5" s="52"/>
     </row>
-    <row r="6" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="21">
       <c r="A6" s="175"/>
       <c r="B6" s="181"/>
       <c r="C6" s="184"/>
       <c r="D6" s="187"/>
       <c r="E6" s="46" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
       <c r="H6" s="48"/>
       <c r="I6" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K6" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L6" s="51"/>
       <c r="M6" s="49"/>
       <c r="N6" s="49"/>
       <c r="O6" s="52"/>
     </row>
-    <row r="7" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="21">
       <c r="A7" s="175"/>
       <c r="B7" s="181"/>
       <c r="C7" s="184"/>
       <c r="D7" s="187"/>
       <c r="E7" s="46" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F7" s="47"/>
       <c r="G7" s="47"/>
       <c r="H7" s="48"/>
       <c r="I7" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K7" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L7" s="51"/>
       <c r="M7" s="49"/>
       <c r="N7" s="49"/>
       <c r="O7" s="52"/>
     </row>
-    <row r="8" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="21">
       <c r="A8" s="175"/>
       <c r="B8" s="181"/>
       <c r="C8" s="184"/>
       <c r="D8" s="187"/>
       <c r="E8" s="46" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F8" s="47"/>
       <c r="G8" s="47"/>
       <c r="H8" s="48"/>
       <c r="I8" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K8" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L8" s="51"/>
       <c r="M8" s="49"/>
       <c r="N8" s="49"/>
       <c r="O8" s="52"/>
     </row>
-    <row r="9" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="21">
       <c r="A9" s="175"/>
       <c r="B9" s="181"/>
       <c r="C9" s="184"/>
       <c r="D9" s="187"/>
       <c r="E9" s="46" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F9" s="47"/>
       <c r="G9" s="47"/>
       <c r="H9" s="48"/>
       <c r="I9" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K9" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L9" s="51"/>
       <c r="M9" s="49"/>
       <c r="N9" s="49"/>
       <c r="O9" s="52"/>
     </row>
-    <row r="10" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="21">
       <c r="A10" s="175"/>
       <c r="B10" s="181"/>
       <c r="C10" s="184"/>
       <c r="D10" s="187"/>
       <c r="E10" s="46" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F10" s="47"/>
       <c r="G10" s="47"/>
       <c r="H10" s="48"/>
       <c r="I10" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K10" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L10" s="51"/>
       <c r="M10" s="49"/>
       <c r="N10" s="49"/>
       <c r="O10" s="52"/>
     </row>
-    <row r="11" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="21">
       <c r="A11" s="175"/>
       <c r="B11" s="181"/>
       <c r="C11" s="184"/>
       <c r="D11" s="187"/>
       <c r="E11" s="46" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F11" s="47"/>
       <c r="G11" s="47"/>
       <c r="H11" s="48"/>
       <c r="I11" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J11" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L11" s="51"/>
       <c r="M11" s="49"/>
       <c r="N11" s="49"/>
       <c r="O11" s="52"/>
     </row>
-    <row r="12" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="21">
       <c r="A12" s="175"/>
       <c r="B12" s="181"/>
       <c r="C12" s="184"/>
       <c r="D12" s="187"/>
       <c r="E12" s="46" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F12" s="47"/>
       <c r="G12" s="47"/>
       <c r="H12" s="48"/>
       <c r="I12" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K12" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L12" s="51"/>
       <c r="M12" s="49"/>
       <c r="N12" s="49"/>
       <c r="O12" s="52"/>
     </row>
-    <row r="13" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="21">
       <c r="A13" s="175"/>
       <c r="B13" s="181"/>
       <c r="C13" s="184"/>
       <c r="D13" s="187"/>
       <c r="E13" s="46" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F13" s="47"/>
       <c r="G13" s="47"/>
       <c r="H13" s="48"/>
       <c r="I13" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L13" s="51"/>
       <c r="M13" s="50"/>
       <c r="N13" s="50"/>
       <c r="O13" s="52"/>
     </row>
-    <row r="14" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="21">
       <c r="A14" s="175"/>
       <c r="B14" s="181"/>
       <c r="C14" s="184"/>
       <c r="D14" s="187"/>
       <c r="E14" s="46" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F14" s="47"/>
       <c r="G14" s="47"/>
       <c r="H14" s="48"/>
       <c r="I14" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L14" s="51"/>
       <c r="M14" s="49"/>
       <c r="N14" s="49"/>
       <c r="O14" s="52"/>
     </row>
-    <row r="15" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="21">
       <c r="A15" s="175"/>
       <c r="B15" s="181"/>
       <c r="C15" s="184"/>
       <c r="D15" s="187"/>
       <c r="E15" s="46" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F15" s="47"/>
       <c r="G15" s="47"/>
       <c r="H15" s="48"/>
       <c r="I15" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L15" s="51"/>
       <c r="M15" s="50"/>
       <c r="N15" s="50"/>
       <c r="O15" s="52"/>
     </row>
-    <row r="16" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="21">
       <c r="A16" s="175"/>
       <c r="B16" s="181"/>
       <c r="C16" s="184"/>
       <c r="D16" s="187"/>
       <c r="E16" s="46" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F16" s="47"/>
       <c r="G16" s="47"/>
       <c r="H16" s="48"/>
       <c r="I16" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K16" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L16" s="51"/>
       <c r="M16" s="49"/>
       <c r="N16" s="49"/>
       <c r="O16" s="52"/>
     </row>
-    <row r="17" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="21">
       <c r="A17" s="175"/>
       <c r="B17" s="181"/>
       <c r="C17" s="184"/>
       <c r="D17" s="187"/>
       <c r="E17" s="46" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F17" s="47"/>
       <c r="G17" s="47"/>
       <c r="H17" s="48"/>
       <c r="I17" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L17" s="51"/>
       <c r="M17" s="49"/>
       <c r="N17" s="49"/>
       <c r="O17" s="52"/>
     </row>
-    <row r="18" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="21">
       <c r="A18" s="175"/>
       <c r="B18" s="181"/>
       <c r="C18" s="184"/>
       <c r="D18" s="187"/>
       <c r="E18" s="46" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F18" s="47"/>
       <c r="G18" s="47"/>
       <c r="H18" s="48"/>
       <c r="I18" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J18" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K18" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L18" s="51"/>
       <c r="M18" s="49"/>
       <c r="N18" s="49"/>
       <c r="O18" s="52"/>
     </row>
-    <row r="19" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="21">
       <c r="A19" s="175"/>
       <c r="B19" s="181"/>
       <c r="C19" s="184"/>
       <c r="D19" s="187"/>
       <c r="E19" s="46" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F19" s="47"/>
       <c r="G19" s="47"/>
       <c r="H19" s="48"/>
       <c r="I19" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L19" s="51"/>
       <c r="M19" s="49"/>
       <c r="N19" s="49"/>
       <c r="O19" s="52"/>
     </row>
-    <row r="20" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="21">
       <c r="A20" s="175"/>
       <c r="B20" s="181"/>
       <c r="C20" s="184"/>
       <c r="D20" s="187"/>
       <c r="E20" s="53" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F20" s="54"/>
       <c r="G20" s="54"/>
       <c r="H20" s="55"/>
       <c r="I20" s="56" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J20" s="56" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K20" s="57" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L20" s="54"/>
       <c r="M20" s="56"/>
       <c r="N20" s="56"/>
       <c r="O20" s="58"/>
     </row>
-    <row r="21" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="21">
       <c r="A21" s="175"/>
       <c r="B21" s="181"/>
       <c r="C21" s="184"/>
       <c r="D21" s="187"/>
       <c r="E21" s="53" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F21" s="54"/>
       <c r="G21" s="54"/>
       <c r="H21" s="55"/>
       <c r="I21" s="56" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J21" s="56" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K21" s="57" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L21" s="54"/>
       <c r="M21" s="56"/>
       <c r="N21" s="56"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" ht="21">
       <c r="A22" s="175"/>
       <c r="B22" s="181"/>
       <c r="C22" s="184"/>
       <c r="D22" s="187"/>
       <c r="E22" s="46" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" s="47" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G22" s="59"/>
       <c r="H22" s="60"/>
       <c r="I22" s="49"/>
       <c r="J22" s="49"/>
       <c r="K22" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L22" s="51"/>
       <c r="M22" s="49"/>
       <c r="N22" s="49"/>
       <c r="O22" s="52"/>
     </row>
-    <row r="23" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" ht="21">
       <c r="A23" s="175"/>
       <c r="B23" s="181"/>
       <c r="C23" s="184"/>
       <c r="D23" s="187"/>
       <c r="E23" s="46" t="s">
+        <v>438</v>
+      </c>
+      <c r="F23" s="47" t="s">
         <v>437</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>436</v>
       </c>
       <c r="G23" s="47"/>
       <c r="H23" s="48"/>
       <c r="I23" s="49"/>
       <c r="J23" s="49"/>
       <c r="K23" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L23" s="51"/>
       <c r="M23" s="49"/>
       <c r="N23" s="49"/>
       <c r="O23" s="52"/>
     </row>
-    <row r="24" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="21">
       <c r="A24" s="175"/>
       <c r="B24" s="181"/>
       <c r="C24" s="184"/>
       <c r="D24" s="187"/>
       <c r="E24" s="46" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F24" s="47" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G24" s="47"/>
       <c r="H24" s="48"/>
       <c r="I24" s="49"/>
       <c r="J24" s="49"/>
       <c r="K24" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L24" s="51"/>
       <c r="M24" s="50"/>
       <c r="N24" s="61"/>
       <c r="O24" s="52"/>
     </row>
-    <row r="25" spans="1:15" ht="21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="21">
       <c r="A25" s="175"/>
       <c r="B25" s="181"/>
       <c r="C25" s="184"/>
       <c r="D25" s="187"/>
       <c r="E25" s="46" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F25" s="47" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G25" s="47"/>
       <c r="H25" s="62"/>
       <c r="I25" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J25" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L25" s="63">
         <v>100</v>
       </c>
       <c r="M25" s="50" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N25" s="50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O25" s="52"/>
     </row>
-    <row r="26" spans="1:15" ht="21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="21">
       <c r="A26" s="175"/>
       <c r="B26" s="181"/>
       <c r="C26" s="184"/>
       <c r="D26" s="187"/>
       <c r="E26" s="46" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F26" s="47" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G26" s="47"/>
       <c r="H26" s="62"/>
       <c r="I26" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J26" s="49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K26" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L26" s="63">
         <v>100</v>
       </c>
       <c r="M26" s="50" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N26" s="50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O26" s="52"/>
     </row>
-    <row r="27" spans="1:15" ht="21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="21">
       <c r="A27" s="175"/>
       <c r="B27" s="181"/>
       <c r="C27" s="184"/>
       <c r="D27" s="187"/>
       <c r="E27" s="46" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G27" s="47"/>
       <c r="H27" s="62"/>
       <c r="I27" s="49"/>
       <c r="J27" s="49"/>
       <c r="K27" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L27" s="63"/>
       <c r="M27" s="64"/>
       <c r="N27" s="64"/>
       <c r="O27" s="52"/>
     </row>
-    <row r="28" spans="1:15" ht="21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="21">
       <c r="A28" s="175"/>
       <c r="B28" s="181"/>
       <c r="C28" s="184"/>
       <c r="D28" s="187"/>
       <c r="E28" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="F28" s="47" t="s">
         <v>445</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>444</v>
       </c>
       <c r="G28" s="47"/>
       <c r="H28" s="62"/>
       <c r="I28" s="49"/>
       <c r="J28" s="49"/>
       <c r="K28" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L28" s="63"/>
       <c r="M28" s="64"/>
       <c r="N28" s="64"/>
       <c r="O28" s="52"/>
     </row>
-    <row r="29" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="18">
       <c r="A29" s="175"/>
       <c r="B29" s="181"/>
       <c r="C29" s="184"/>
       <c r="D29" s="187"/>
       <c r="E29" s="46" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F29" s="65" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G29" s="65"/>
       <c r="H29" s="49"/>
       <c r="I29" s="49"/>
       <c r="J29" s="49"/>
       <c r="K29" s="50" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L29" s="62" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M29" s="64"/>
       <c r="N29" s="64"/>
       <c r="O29" s="52"/>
     </row>
-    <row r="30" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="18.399999999999999" thickBot="1">
       <c r="A30" s="176"/>
       <c r="B30" s="182"/>
       <c r="C30" s="185"/>
       <c r="D30" s="188"/>
       <c r="E30" s="66" t="s">
+        <v>449</v>
+      </c>
+      <c r="F30" s="67" t="s">
         <v>448</v>
-      </c>
-      <c r="F30" s="67" t="s">
-        <v>447</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="68"/>
       <c r="I30" s="68"/>
       <c r="J30" s="69"/>
       <c r="K30" s="70" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L30" s="71" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M30" s="70"/>
       <c r="N30" s="70"/>
@@ -9311,125 +9068,125 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="99.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="135.6640625" customWidth="1"/>
+    <col min="1" max="1" width="99.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="135.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="12" customFormat="1">
       <c r="A1" s="24" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="21"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="21"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="21"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="21"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="21"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="21"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="21"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="C9" s="25"/>
       <c r="D9" s="21"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="C10" s="25"/>
       <c r="D10" s="21"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="22" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C11" s="25"/>
       <c r="D11" s="21"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="21"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="21"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="21"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="C15" s="25"/>
       <c r="D15" s="21"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="21"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4">
       <c r="C17" s="25"/>
       <c r="D17" s="21"/>
     </row>
@@ -9445,389 +9202,389 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="99.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="23" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="135.6640625" customWidth="1"/>
+    <col min="1" max="1" width="99.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="135.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="12" customFormat="1">
       <c r="A1" s="24" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="21"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="21"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="C4" s="25"/>
       <c r="D4" s="21"/>
     </row>
-    <row r="5" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" s="12" customFormat="1">
       <c r="A5" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B5" s="27"/>
       <c r="C5" s="28"/>
     </row>
-    <row r="6" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" s="12" customFormat="1">
       <c r="A6" s="29" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="25"/>
       <c r="D6" s="21"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="21"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="15" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="21"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="15" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="21"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="C10" s="25"/>
       <c r="D10" s="21"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="C11" s="25"/>
       <c r="D11" s="21"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="C12" s="25"/>
       <c r="D12" s="21"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="31" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="25"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C14" s="25"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="15" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C15" s="25"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="15" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C16" s="25"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C17" s="25"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="15" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C18" s="25"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="15" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C19" s="25"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="15" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C20" s="25"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C21" s="25"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="25"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="25"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="25"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="25"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="25"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C27" s="25"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="C28" s="25"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C29" s="25"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="15" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C30" s="25"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="15" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C31" s="25"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="15" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C32" s="25"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="22" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C33" s="25"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C34" s="25"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C35" s="25"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C36" s="25"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C37" s="25"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C38" s="25"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C39" s="25"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C40" s="25"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="15" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C41" s="25"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C42" s="25"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="C43" s="25"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" s="31" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C44" s="25"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" s="15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C45" s="25"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C46" s="25"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" s="15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C47" s="25"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" s="15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C48" s="25"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49" s="15" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C49" s="25"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50" s="15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C50" s="25"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51" s="15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C51" s="25"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52" s="15" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C52" s="25"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4">
       <c r="A53" s="15" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C53" s="25"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4">
       <c r="A54" s="15" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C54" s="25"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55" s="15" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C55" s="25"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="A56" s="15" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C56" s="25"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57" s="34" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C57" s="25"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58" s="34" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C58" s="25"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="A59" s="35" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C59" s="25"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="A60" s="35" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C60" s="25"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="C61" s="25"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4">
       <c r="A62" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C62" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -9842,188 +9599,188 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="99.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="135.6640625" customWidth="1"/>
+    <col min="1" max="1" width="99.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="135.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="12" customFormat="1">
       <c r="A1" s="24" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="21"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C3" s="25">
         <v>1</v>
       </c>
       <c r="D3" s="21"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="C4" s="25"/>
       <c r="D4" s="21"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="21"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="21"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="15" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="21"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C8" s="25"/>
       <c r="D8" s="21"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="21"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="15"/>
       <c r="C10" s="25"/>
       <c r="D10" s="21"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C11" s="25"/>
       <c r="D11" s="21"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="21"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="21"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="21"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="15"/>
       <c r="C15" s="25"/>
       <c r="D15" s="21"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="37" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="21"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="21"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="21"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="15" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C19" s="25"/>
       <c r="D19" s="21"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="21"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="21"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="21"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" s="15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="21"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" s="15" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -10038,412 +9795,412 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:D64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="99.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="135.6640625" customWidth="1"/>
+    <col min="1" max="1" width="99.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="135.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="12" customFormat="1">
       <c r="A1" s="24" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C2" s="25"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C3" s="25"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C4" s="25"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="15"/>
       <c r="C5" s="25"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="37" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C6" s="25"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C7" s="25"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C8" s="25"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="29" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C9" s="25"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="29" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C10" s="25"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C11" s="25"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="15" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C12" s="25"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="15" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C13" s="25"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="15"/>
       <c r="C14" s="25"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="22" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C15" s="25"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C16" s="25"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="15" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C17" s="25"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C18" s="25"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C19" s="25"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="25"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="25"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="25"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C23" s="25"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C24" s="25"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C25" s="25"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C26" s="25"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="15"/>
       <c r="C27" s="25"/>
     </row>
-    <row r="28" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" s="22" customFormat="1">
       <c r="A28" s="22" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="28"/>
     </row>
-    <row r="29" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" s="22" customFormat="1">
       <c r="A29" s="15" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="28"/>
     </row>
-    <row r="30" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" s="22" customFormat="1">
       <c r="A30" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="28"/>
     </row>
-    <row r="31" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" s="22" customFormat="1">
       <c r="A31" s="15" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="28"/>
     </row>
-    <row r="32" spans="1:3" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" s="22" customFormat="1">
       <c r="A32" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="28"/>
     </row>
-    <row r="33" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" s="22" customFormat="1">
       <c r="A33" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="28"/>
     </row>
-    <row r="34" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" s="22" customFormat="1">
       <c r="B34" s="12"/>
       <c r="C34" s="38"/>
       <c r="D34" s="31"/>
     </row>
-    <row r="35" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" s="22" customFormat="1">
       <c r="A35" s="22" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="28"/>
     </row>
-    <row r="36" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" s="22" customFormat="1">
       <c r="A36" s="15" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="28"/>
     </row>
-    <row r="37" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" s="22" customFormat="1">
       <c r="A37" s="15" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="28"/>
     </row>
-    <row r="38" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" s="22" customFormat="1">
       <c r="A38" s="15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="28"/>
     </row>
-    <row r="39" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" s="22" customFormat="1">
       <c r="B39" s="12"/>
       <c r="C39" s="38"/>
       <c r="D39" s="31"/>
     </row>
-    <row r="40" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" s="22" customFormat="1">
       <c r="A40" s="22" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="38"/>
       <c r="D40" s="31"/>
     </row>
-    <row r="41" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" s="22" customFormat="1">
       <c r="A41" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B41" s="12"/>
       <c r="C41" s="38"/>
       <c r="D41" s="31"/>
     </row>
-    <row r="42" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" s="22" customFormat="1">
       <c r="A42" s="15" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B42" s="12"/>
       <c r="C42" s="38"/>
       <c r="D42" s="31"/>
     </row>
-    <row r="43" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" s="22" customFormat="1">
       <c r="B43" s="12"/>
       <c r="C43" s="38"/>
       <c r="D43" s="31"/>
     </row>
-    <row r="44" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" s="22" customFormat="1">
       <c r="A44" s="37" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="38"/>
       <c r="D44" s="31"/>
     </row>
-    <row r="45" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" s="22" customFormat="1">
       <c r="A45" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B45" s="12"/>
       <c r="C45" s="38"/>
       <c r="D45" s="31"/>
     </row>
-    <row r="46" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" s="22" customFormat="1">
       <c r="A46" s="15" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B46" s="12"/>
       <c r="C46" s="38"/>
       <c r="D46" s="31"/>
     </row>
-    <row r="47" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" s="22" customFormat="1">
       <c r="B47" s="12"/>
       <c r="C47" s="38"/>
       <c r="D47" s="31"/>
     </row>
-    <row r="48" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" s="22" customFormat="1">
       <c r="A48" s="37" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B48" s="12"/>
       <c r="C48" s="38"/>
       <c r="D48" s="31"/>
     </row>
-    <row r="49" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" s="22" customFormat="1">
       <c r="A49" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="38"/>
       <c r="D49" s="31"/>
     </row>
-    <row r="50" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" s="22" customFormat="1">
       <c r="A50" s="15" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B50" s="12"/>
       <c r="C50" s="38"/>
       <c r="D50" s="31"/>
     </row>
-    <row r="51" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" s="22" customFormat="1">
       <c r="A51" s="15" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="38"/>
       <c r="D51" s="31"/>
     </row>
-    <row r="52" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" s="22" customFormat="1">
       <c r="B52" s="12"/>
       <c r="C52" s="38"/>
       <c r="D52" s="31"/>
     </row>
-    <row r="53" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" s="22" customFormat="1">
       <c r="B53" s="12"/>
       <c r="C53" s="38"/>
       <c r="D53" s="31"/>
     </row>
-    <row r="54" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" s="22" customFormat="1">
       <c r="A54" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="38"/>
       <c r="D54" s="31"/>
     </row>
-    <row r="55" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" s="22" customFormat="1">
       <c r="A55" s="15" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B55" s="12"/>
       <c r="C55" s="38"/>
       <c r="D55" s="31"/>
     </row>
-    <row r="56" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" s="22" customFormat="1">
       <c r="A56" s="15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B56" s="12"/>
       <c r="C56" s="38"/>
       <c r="D56" s="31"/>
     </row>
-    <row r="57" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" s="22" customFormat="1">
       <c r="B57" s="12"/>
       <c r="C57" s="38"/>
       <c r="D57" s="31"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58" s="22" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C58" s="25"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="C59" s="25"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="A60" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C60" s="25"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="C61" s="25"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4">
       <c r="C62" s="25"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4">
       <c r="C63" s="25"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4">
       <c r="C64" s="25"/>
     </row>
   </sheetData>
@@ -10458,15 +10215,15 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" style="18" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" style="18" customWidth="1"/>
     <col min="3" max="3" width="86" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="124" t="s">
         <v>80</v>
       </c>
@@ -10498,17 +10255,17 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="14.65" thickBot="1">
       <c r="A1" s="87" t="s">
         <v>84</v>
       </c>
@@ -10528,7 +10285,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="88">
         <v>2023</v>
       </c>
@@ -10544,7 +10301,7 @@
       <c r="E2" s="88"/>
       <c r="F2" s="88"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="88">
         <v>2024</v>
       </c>
@@ -10562,7 +10319,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="88"/>
       <c r="B4" s="88"/>
       <c r="C4" s="88"/>
@@ -10570,7 +10327,7 @@
       <c r="E4" s="88"/>
       <c r="F4" s="88"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="88"/>
       <c r="B5" s="88"/>
       <c r="C5" s="88"/>
@@ -10578,7 +10335,7 @@
       <c r="E5" s="88"/>
       <c r="F5" s="88"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="88"/>
       <c r="B6" s="88"/>
       <c r="C6" s="88"/>
@@ -10586,7 +10343,7 @@
       <c r="E6" s="88"/>
       <c r="F6" s="88"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="88"/>
       <c r="B7" s="88"/>
       <c r="C7" s="88"/>
@@ -10594,7 +10351,7 @@
       <c r="E7" s="88"/>
       <c r="F7" s="88"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="88"/>
       <c r="B8" s="88"/>
       <c r="C8" s="88"/>
@@ -10617,21 +10374,21 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="B1:E104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="0.88671875" customWidth="1"/>
-    <col min="2" max="2" width="71.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:3" ht="5.25" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:3" ht="14.65" thickBot="1">
       <c r="B2" s="167" t="s">
         <v>92</v>
       </c>
       <c r="C2" s="168"/>
     </row>
-    <row r="3" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" ht="14.65" thickTop="1">
       <c r="B3" s="5" t="s">
         <v>93</v>
       </c>
@@ -10639,7 +10396,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3">
       <c r="B4" s="5" t="s">
         <v>95</v>
       </c>
@@ -10647,7 +10404,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3">
       <c r="B5" s="5" t="s">
         <v>97</v>
       </c>
@@ -10655,7 +10412,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3">
       <c r="B6" s="1" t="s">
         <v>99</v>
       </c>
@@ -10663,7 +10420,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3">
       <c r="B7" s="1" t="s">
         <v>101</v>
       </c>
@@ -10671,7 +10428,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3">
       <c r="B8" s="1" t="s">
         <v>103</v>
       </c>
@@ -10679,7 +10436,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3">
       <c r="B9" s="1" t="s">
         <v>105</v>
       </c>
@@ -10687,92 +10444,92 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3">
       <c r="B10" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3">
       <c r="B11" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3">
       <c r="B12" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3">
       <c r="B13" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3">
       <c r="B14" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3">
       <c r="B15" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3">
       <c r="B16" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5">
       <c r="B17" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5">
       <c r="B18" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5">
       <c r="B19" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5">
       <c r="B20" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5">
       <c r="B21" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5">
       <c r="B22" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" ht="14.65" thickBot="1">
       <c r="B23" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" ht="14.65" thickBot="1"/>
+    <row r="25" spans="2:5" ht="14.65" thickBot="1">
       <c r="B25" s="167" t="s">
         <v>121</v>
       </c>
@@ -10781,384 +10538,384 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" ht="14.65" thickTop="1">
       <c r="B26" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C26" s="6"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5">
       <c r="B27" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5">
       <c r="B28" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5">
       <c r="B29" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5">
       <c r="B30" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5">
       <c r="B31" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5">
       <c r="B32" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3">
       <c r="B33" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3">
       <c r="B34" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3">
       <c r="B35" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3">
       <c r="B36" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3">
       <c r="B37" s="73" t="s">
         <v>126</v>
       </c>
       <c r="C37" s="19"/>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3">
       <c r="B38" s="73" t="s">
         <v>120</v>
       </c>
       <c r="C38" s="19"/>
     </row>
-    <row r="39" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:3" ht="14.65" thickBot="1">
       <c r="B39" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:3" ht="14.65" thickBot="1"/>
+    <row r="41" spans="2:3" ht="14.65" thickBot="1">
       <c r="B41" s="169" t="s">
         <v>128</v>
       </c>
       <c r="C41" s="170"/>
     </row>
-    <row r="42" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:3" ht="14.65" thickTop="1">
       <c r="B42" s="5" t="s">
         <v>129</v>
       </c>
       <c r="C42" s="6"/>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:3">
       <c r="B43" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C43" s="3"/>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:3">
       <c r="B44" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:3">
       <c r="B45" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C45" s="3"/>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:3">
       <c r="B47" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C47" s="3"/>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:3">
       <c r="B48" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3">
       <c r="B49" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3">
       <c r="B50" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C50" s="19"/>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3">
       <c r="B51" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C51" s="19"/>
     </row>
-    <row r="52" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:3" ht="14.65" thickBot="1">
       <c r="B52" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C52" s="4"/>
     </row>
-    <row r="53" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="54" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:3" ht="14.65" thickBot="1"/>
+    <row r="54" spans="2:3" ht="14.65" thickBot="1">
       <c r="B54" s="169" t="s">
         <v>140</v>
       </c>
       <c r="C54" s="170"/>
     </row>
-    <row r="55" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:3" ht="14.65" thickTop="1">
       <c r="B55" s="5" t="s">
         <v>141</v>
       </c>
       <c r="C55" s="6"/>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3">
       <c r="B56" s="5" t="s">
         <v>142</v>
       </c>
       <c r="C56" s="6"/>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3">
       <c r="B57" s="5" t="s">
         <v>143</v>
       </c>
       <c r="C57" s="6"/>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3">
       <c r="B58" s="5" t="s">
         <v>144</v>
       </c>
       <c r="C58" s="6"/>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:3">
       <c r="B59" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:3" ht="14.65" thickBot="1"/>
+    <row r="61" spans="2:3" ht="14.65" thickBot="1">
       <c r="B61" s="167" t="s">
         <v>146</v>
       </c>
       <c r="C61" s="168"/>
     </row>
-    <row r="62" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" ht="14.65" thickTop="1">
       <c r="B62" s="5" t="s">
         <v>147</v>
       </c>
       <c r="C62" s="6"/>
     </row>
-    <row r="63" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:3" ht="14.65" thickBot="1">
       <c r="C63" s="15"/>
     </row>
-    <row r="64" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:3" ht="14.65" thickBot="1">
       <c r="B64" s="169" t="s">
         <v>148</v>
       </c>
       <c r="C64" s="170"/>
     </row>
-    <row r="65" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:3" ht="14.65" thickTop="1">
       <c r="B65" s="5" t="s">
         <v>149</v>
       </c>
       <c r="C65" s="6"/>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:3">
       <c r="B66" s="5" t="s">
         <v>150</v>
       </c>
       <c r="C66" s="6"/>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:3">
       <c r="B67" s="5" t="s">
         <v>151</v>
       </c>
       <c r="C67" s="6"/>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:3">
       <c r="B68" s="5" t="s">
         <v>152</v>
       </c>
       <c r="C68" s="6"/>
     </row>
-    <row r="69" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:3" ht="14.65" thickBot="1"/>
+    <row r="70" spans="2:3" ht="14.65" thickBot="1">
       <c r="B70" s="167" t="s">
         <v>153</v>
       </c>
       <c r="C70" s="168"/>
     </row>
-    <row r="71" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:3" ht="14.65" thickTop="1">
       <c r="B71" s="5"/>
       <c r="C71" s="6"/>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:3">
       <c r="B72" s="1"/>
       <c r="C72" s="3"/>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:3">
       <c r="B73" s="1"/>
       <c r="C73" s="3"/>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:3">
       <c r="B74" s="1"/>
       <c r="C74" s="3"/>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:3">
       <c r="B75" s="1"/>
       <c r="C75" s="3"/>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:3">
       <c r="B76" s="1"/>
       <c r="C76" s="3"/>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:3">
       <c r="B77" s="1"/>
       <c r="C77" s="3"/>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:3">
       <c r="B78" s="1"/>
       <c r="C78" s="3"/>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:3">
       <c r="B79" s="1"/>
       <c r="C79" s="3"/>
     </row>
-    <row r="80" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:3" ht="14.65" thickBot="1">
       <c r="B80" s="2"/>
       <c r="C80" s="4"/>
     </row>
-    <row r="81" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:3" ht="14.65" thickBot="1"/>
+    <row r="82" spans="2:3" ht="14.65" thickBot="1">
       <c r="B82" s="167" t="s">
         <v>154</v>
       </c>
       <c r="C82" s="168"/>
     </row>
-    <row r="83" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:3" ht="14.65" thickTop="1">
       <c r="B83" s="5"/>
       <c r="C83" s="6"/>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:3">
       <c r="B84" s="1"/>
       <c r="C84" s="3"/>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:3">
       <c r="B85" s="1"/>
       <c r="C85" s="3"/>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:3">
       <c r="B86" s="1"/>
       <c r="C86" s="3"/>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:3">
       <c r="B87" s="1"/>
       <c r="C87" s="3"/>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:3">
       <c r="B88" s="1"/>
       <c r="C88" s="3"/>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:3">
       <c r="B89" s="1"/>
       <c r="C89" s="3"/>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:3">
       <c r="B90" s="1"/>
       <c r="C90" s="3"/>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:3">
       <c r="B91" s="1"/>
       <c r="C91" s="3"/>
     </row>
-    <row r="92" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:3" ht="14.65" thickBot="1">
       <c r="B92" s="2"/>
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="94" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:3" ht="14.65" thickBot="1"/>
+    <row r="94" spans="2:3" ht="14.65" thickBot="1">
       <c r="B94" s="167" t="s">
         <v>155</v>
       </c>
       <c r="C94" s="168"/>
     </row>
-    <row r="95" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:3" ht="14.65" thickTop="1">
       <c r="B95" s="5"/>
       <c r="C95" s="6"/>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:3">
       <c r="B96" s="1"/>
       <c r="C96" s="3"/>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:3">
       <c r="B97" s="1"/>
       <c r="C97" s="3"/>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:3">
       <c r="B98" s="1"/>
       <c r="C98" s="3"/>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:3">
       <c r="B99" s="1"/>
       <c r="C99" s="3"/>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:3">
       <c r="B100" s="1"/>
       <c r="C100" s="3"/>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:3">
       <c r="B101" s="1"/>
       <c r="C101" s="3"/>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:3">
       <c r="B102" s="1"/>
       <c r="C102" s="3"/>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:3">
       <c r="B103" s="1"/>
       <c r="C103" s="3"/>
     </row>
-    <row r="104" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:3" ht="14.65" thickBot="1">
       <c r="B104" s="2"/>
       <c r="C104" s="4"/>
     </row>
@@ -11184,967 +10941,405 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B66"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="65.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="84" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="65.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="12" customFormat="1">
       <c r="A1" s="11" t="s">
         <v>156</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>561</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>596</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>610</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="G2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B3" s="15"/>
-      <c r="C3" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B4" s="15"/>
-      <c r="C4" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B5" s="15"/>
-      <c r="C5" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>582</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>582</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B7" s="15"/>
-      <c r="C7" s="15" t="s">
-        <v>566</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>611</v>
-      </c>
-      <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B9" s="15"/>
-      <c r="C9" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>584</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>597</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>612</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="15"/>
-      <c r="C10" s="15" t="s">
-        <v>568</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="G10" s="15"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B11" s="15"/>
-      <c r="C11" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>599</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B12" s="15"/>
-      <c r="C12" s="15" t="s">
-        <v>570</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>570</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" s="15"/>
-      <c r="C13" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>600</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" s="15"/>
-      <c r="C15" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="13"/>
       <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B19" s="15"/>
-      <c r="C19" s="15" t="s">
-        <v>573</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B20" s="15"/>
-      <c r="C20" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>603</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="G21" s="15"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15" t="s">
-        <v>604</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B23" s="15"/>
-      <c r="C23" s="15" t="s">
-        <v>575</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>605</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>606</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="13"/>
       <c r="B42" s="89"/>
-      <c r="C42" s="89"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B44" s="15"/>
-      <c r="C44" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="G44" s="15"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B45" s="15"/>
-      <c r="C45" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>594</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>607</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>613</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B46" s="15"/>
-      <c r="C46" s="15" t="s">
-        <v>578</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B47" s="15"/>
-      <c r="C47" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B50" s="15"/>
-      <c r="C50" s="15" t="s">
-        <v>579</v>
-      </c>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15" t="s">
-        <v>579</v>
-      </c>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B51" s="15"/>
-      <c r="C51" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15" t="s">
-        <v>608</v>
-      </c>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15" t="s">
-        <v>609</v>
-      </c>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -12169,297 +11364,297 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
-    <col min="4" max="4" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="14.65" thickBot="1">
       <c r="A1" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="14.65" thickTop="1">
       <c r="A2" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F2" s="10"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="31"/>
       <c r="D3" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F3" s="10"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>230</v>
-      </c>
       <c r="C4" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="B5" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="D5" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>235</v>
-      </c>
       <c r="B7" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>237</v>
-      </c>
       <c r="F7" s="10"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F16" s="10"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F17" s="10"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -12467,13 +11662,13 @@
         <v>17</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F18" s="10"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -12481,9 +11676,9 @@
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -12491,139 +11686,139 @@
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
         <v>73</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F21" s="10"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F23" s="10"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F24" s="10"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C29" s="10">
         <v>12345</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="10" t="s">
         <v>253</v>
-      </c>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>0</v>
@@ -12632,64 +11827,64 @@
         <v>112233</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>0</v>
       </c>
       <c r="F30" s="10"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F31" s="10"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F31" s="10"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
-        <v>256</v>
-      </c>
       <c r="B32" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="E32" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="E32" s="10" t="s">
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>258</v>
-      </c>
       <c r="E33" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F33" s="10"/>
     </row>
@@ -12707,29 +11902,29 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:G53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" customWidth="1"/>
-    <col min="2" max="2" width="35.88671875" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="50.42578125" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="22" customFormat="1">
       <c r="A1" s="40" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E1" s="172" t="s">
         <v>38</v>
@@ -12737,7 +11932,7 @@
       <c r="F1" s="172"/>
       <c r="G1" s="172"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -12746,7 +11941,7 @@
       <c r="F2" s="173"/>
       <c r="G2" s="173"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -12755,7 +11950,7 @@
       <c r="F3" s="173"/>
       <c r="G3" s="173"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -12764,7 +11959,7 @@
       <c r="F4" s="173"/>
       <c r="G4" s="173"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -12773,7 +11968,7 @@
       <c r="F5" s="173"/>
       <c r="G5" s="173"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -12782,7 +11977,7 @@
       <c r="F6" s="173"/>
       <c r="G6" s="173"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -12791,7 +11986,7 @@
       <c r="F7" s="173"/>
       <c r="G7" s="173"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -12800,18 +11995,18 @@
       <c r="F8" s="173"/>
       <c r="G8" s="173"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E10" s="172" t="s">
         <v>38</v>
@@ -12819,7 +12014,7 @@
       <c r="F10" s="172"/>
       <c r="G10" s="172"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -12828,7 +12023,7 @@
       <c r="F11" s="171"/>
       <c r="G11" s="171"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -12837,7 +12032,7 @@
       <c r="F12" s="171"/>
       <c r="G12" s="171"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -12846,7 +12041,7 @@
       <c r="F13" s="171"/>
       <c r="G13" s="171"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -12855,163 +12050,163 @@
       <c r="F14" s="171"/>
       <c r="G14" s="171"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B16" s="39"/>
       <c r="C16" s="12"/>
       <c r="F16" s="172" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G16" s="172"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B17" s="39"/>
       <c r="C17" s="12"/>
       <c r="F17" s="40" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G17" s="17"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B18" s="39"/>
       <c r="F18" s="40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G18" s="17"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" s="41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B19" s="39"/>
       <c r="D19" s="15"/>
       <c r="F19" s="40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" s="41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B20" s="39">
         <v>38400</v>
       </c>
       <c r="D20" s="15"/>
       <c r="F20" s="40" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G20" s="17"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" s="41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G21" s="17"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" s="42"/>
       <c r="B22" s="15"/>
       <c r="F22" s="40" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G22" s="17"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" s="41" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B23" s="39"/>
       <c r="F23" s="40" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G23" s="17"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" s="41" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B24" s="39"/>
       <c r="F24" s="40" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G24" s="17"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="41" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B25" s="39"/>
       <c r="F25" s="40" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G25" s="17"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" s="41" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B26" s="39"/>
       <c r="C26" s="41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D26" s="17"/>
       <c r="F26" s="40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G26" s="17"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" s="41" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B27" s="39"/>
       <c r="C27" s="41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D27" s="17"/>
       <c r="F27" s="40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G27" s="17"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" s="41" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D28" s="17"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29" s="41" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D29" s="17"/>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="5:5">
       <c r="E53" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -13044,50 +12239,50 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.88671875" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="15" customFormat="1">
       <c r="A1" s="40" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G1" s="40" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1" s="40" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I1" s="40" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J1" s="40" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -13099,7 +12294,7 @@
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -13111,7 +12306,7 @@
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -13123,7 +12318,7 @@
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -13135,7 +12330,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -13147,7 +12342,7 @@
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -13159,7 +12354,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -13171,7 +12366,7 @@
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -13183,7 +12378,7 @@
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -13195,7 +12390,7 @@
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -13207,7 +12402,7 @@
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -13219,7 +12414,7 @@
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -13231,7 +12426,7 @@
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -13243,7 +12438,7 @@
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -13255,7 +12450,7 @@
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -13267,7 +12462,7 @@
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -13290,118 +12485,118 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:T5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="22" customFormat="1">
       <c r="A1" s="75" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B1" s="75" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1" s="75" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D1" s="75" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E1" s="75" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F1" s="75" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G1" s="75" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1" s="75" t="s">
+        <v>316</v>
+      </c>
+      <c r="I1" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="I1" s="75" t="s">
-        <v>314</v>
-      </c>
       <c r="J1" s="75" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K1" s="75" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L1" s="75" t="s">
+        <v>319</v>
+      </c>
+      <c r="M1" s="75" t="s">
         <v>318</v>
       </c>
-      <c r="M1" s="75" t="s">
-        <v>317</v>
-      </c>
       <c r="N1" s="75" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O1" s="75" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P1" s="75" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q1" s="75" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R1" s="75" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="S1" s="75" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T1" s="75" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="17">
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D2" s="17">
         <v>1</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G2" s="17">
         <v>1</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I2" s="17">
         <v>3</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="17"/>
@@ -13414,36 +12609,36 @@
       <c r="S2" s="17"/>
       <c r="T2" s="17"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20">
       <c r="A3" s="17">
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D3" s="17">
         <v>2</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G3" s="17">
         <v>2</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I3" s="17">
         <v>4</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -13456,36 +12651,36 @@
       <c r="S3" s="17"/>
       <c r="T3" s="17"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20">
       <c r="A4" s="17">
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D4" s="17">
         <v>3</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G4" s="17">
         <v>5</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I4" s="17">
         <v>7</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
@@ -13498,36 +12693,36 @@
       <c r="S4" s="17"/>
       <c r="T4" s="17"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20">
       <c r="A5" s="17">
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D5" s="17">
         <v>4</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G5" s="17">
         <v>6</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I5" s="17">
         <v>8</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
@@ -13546,26 +12741,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22764f65-1f91-4a58-a50d-6cbce21eca12">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2ed2b115-6c2d-4b9d-a375-5d76b684fbe0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009D3D2C266739E043BB3C66B24F8BE822" ma:contentTypeVersion="18" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="9bef219f8659a403fd2b4538d829c5c0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="22764f65-1f91-4a58-a50d-6cbce21eca12" xmlns:ns3="2ed2b115-6c2d-4b9d-a375-5d76b684fbe0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54c6c6508fa9e165dbd1580384fc0569" ns2:_="" ns3:_="">
     <xsd:import namespace="22764f65-1f91-4a58-a50d-6cbce21eca12"/>
@@ -13820,40 +12995,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22764f65-1f91-4a58-a50d-6cbce21eca12">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2ed2b115-6c2d-4b9d-a375-5d76b684fbe0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DCFF404-3738-433F-AD84-3B77DF781E8C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22764f65-1f91-4a58-a50d-6cbce21eca12"/>
-    <ds:schemaRef ds:uri="2ed2b115-6c2d-4b9d-a375-5d76b684fbe0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB0A7BAC-FB1D-4FAC-81C3-3C6C450E4559}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D662CF7-B982-420B-98E9-B390F79A689D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D662CF7-B982-420B-98E9-B390F79A689D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB0A7BAC-FB1D-4FAC-81C3-3C6C450E4559}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="22764f65-1f91-4a58-a50d-6cbce21eca12"/>
-    <ds:schemaRef ds:uri="2ed2b115-6c2d-4b9d-a375-5d76b684fbe0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DCFF404-3738-433F-AD84-3B77DF781E8C}"/>
 </file>